--- a/словари/взаимоотношения.xlsx
+++ b/словари/взаимоотношения.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834E715F-8249-41BA-A434-46381049B688}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B7AEB8-EAD8-4B28-831B-99D2E1FAFE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Неизменные" sheetId="1" r:id="rId1"/>
+    <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
+    <sheet name="Неизменные" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,12 +29,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Этот формат отношений похож</t>
   </si>
   <si>
     <t>Это расширение отношений похоже</t>
+  </si>
+  <si>
+    <t>Пикап, соблазнение</t>
+  </si>
+  <si>
+    <t>Соблазнение</t>
+  </si>
+  <si>
+    <t>Этот текст, который вы скинули даме, предназначен</t>
+  </si>
+  <si>
+    <t>Эта письменность, которую вы скинули женщине, пред-назначена</t>
+  </si>
+  <si>
+    <t>долгосрочный комфорт, причём такой, который улучшил</t>
+  </si>
+  <si>
+    <t>долгосрочное удобство, причём такое, которое улучшило</t>
   </si>
 </sst>
 </file>
@@ -351,19 +370,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.7265625" customWidth="1"/>
-    <col min="2" max="2" width="28.08984375" customWidth="1"/>
+    <col min="1" max="1" width="59.140625" customWidth="1"/>
+    <col min="2" max="2" width="28.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4548B0D-7D71-4248-BE5A-4CF5325314DF}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="77.7109375" customWidth="1"/>
+    <col min="2" max="2" width="65.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/словари/взаимоотношения.xlsx
+++ b/словари/взаимоотношения.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B7AEB8-EAD8-4B28-831B-99D2E1FAFE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992FCBA3-EA04-421D-A98B-536E0F30B586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Этот формат отношений похож</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>долгосрочное удобство, причём такое, которое улучшило</t>
+  </si>
+  <si>
+    <t>пригласил женщину в кафе</t>
+  </si>
+  <si>
+    <t>пригласил женщину в закусочную</t>
   </si>
 </sst>
 </file>
@@ -370,11 +376,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="59.140625" customWidth="1"/>
-    <col min="2" max="2" width="28.140625" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -391,6 +397,14 @@
       </c>
       <c r="B2" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/словари/взаимоотношения.xlsx
+++ b/словари/взаимоотношения.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{992FCBA3-EA04-421D-A98B-536E0F30B586}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9903C7D-D628-4AFE-85C4-5830B5CA2F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Этот формат отношений похож</t>
   </si>
@@ -59,6 +59,12 @@
   </si>
   <si>
     <t>пригласил женщину в закусочную</t>
+  </si>
+  <si>
+    <t>свалившийся с неба коллоквиум</t>
+  </si>
+  <si>
+    <t>с-валившуюся с неба проверку знаний</t>
   </si>
 </sst>
 </file>
@@ -376,14 +382,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="59.140625" customWidth="1"/>
-    <col min="2" max="2" width="43.42578125" customWidth="1"/>
+    <col min="1" max="1" width="59.1796875" customWidth="1"/>
+    <col min="2" max="2" width="43.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -391,7 +397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -399,12 +405,20 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -415,13 +429,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4548B0D-7D71-4248-BE5A-4CF5325314DF}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="77.7109375" customWidth="1"/>
-    <col min="2" max="2" width="65.7109375" customWidth="1"/>
+    <col min="1" max="1" width="77.7265625" customWidth="1"/>
+    <col min="2" max="2" width="65.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -429,7 +443,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>

--- a/словари/взаимоотношения.xlsx
+++ b/словари/взаимоотношения.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9903C7D-D628-4AFE-85C4-5830B5CA2F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D94A47-74ED-470E-8AE0-EF4BDB7335FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57710" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Этот формат отношений похож</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t>с-валившуюся с неба проверку знаний</t>
+  </si>
+  <si>
+    <t>тот формат отношений, который</t>
+  </si>
+  <si>
+    <t>то расширение отношений, которое</t>
   </si>
 </sst>
 </file>
@@ -382,14 +388,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.1796875" customWidth="1"/>
-    <col min="2" max="2" width="43.453125" customWidth="1"/>
+    <col min="1" max="1" width="59.140625" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -397,7 +403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -405,7 +411,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -413,12 +419,20 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -429,13 +443,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4548B0D-7D71-4248-BE5A-4CF5325314DF}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="77.7265625" customWidth="1"/>
-    <col min="2" max="2" width="65.7265625" customWidth="1"/>
+    <col min="1" max="1" width="77.7109375" customWidth="1"/>
+    <col min="2" max="2" width="65.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -443,7 +457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>

--- a/словари/взаимоотношения.xlsx
+++ b/словари/взаимоотношения.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D94A47-74ED-470E-8AE0-EF4BDB7335FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4962A45F-3960-4FF4-A945-543763C840A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-52120" yWindow="2960" windowWidth="27220" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Этот формат отношений похож</t>
   </si>
@@ -71,6 +71,30 @@
   </si>
   <si>
     <t>то расширение отношений, которое</t>
+  </si>
+  <si>
+    <t>Интим я люблю, но он</t>
+  </si>
+  <si>
+    <t>Соитие я люблю, но оно</t>
+  </si>
+  <si>
+    <t>Ситуация с её браком вышла</t>
+  </si>
+  <si>
+    <t>Случай с её браком вышел</t>
+  </si>
+  <si>
+    <t>тот формат отношений, который мне нужен</t>
+  </si>
+  <si>
+    <t>то расширение отношений, которое мне нужно</t>
+  </si>
+  <si>
+    <t>формат отношений чётко не обозначен</t>
+  </si>
+  <si>
+    <t>расширение отношений чётко не обозначено</t>
   </si>
 </sst>
 </file>
@@ -388,14 +412,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="59.140625" customWidth="1"/>
-    <col min="2" max="2" width="43.42578125" customWidth="1"/>
+    <col min="1" max="1" width="59.1796875" customWidth="1"/>
+    <col min="2" max="2" width="43.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -403,7 +427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -411,7 +435,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -419,7 +443,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -427,12 +451,36 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -442,14 +490,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4548B0D-7D71-4248-BE5A-4CF5325314DF}">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="77.7109375" customWidth="1"/>
-    <col min="2" max="2" width="65.7109375" customWidth="1"/>
+    <col min="1" max="1" width="77.7265625" customWidth="1"/>
+    <col min="2" max="2" width="65.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -457,12 +505,20 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/словари/взаимоотношения.xlsx
+++ b/словари/взаимоотношения.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rust\text_changer2\словари\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\rust\text_changer\словари\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4962A45F-3960-4FF4-A945-543763C840A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E484AF-F775-44B3-B27E-DAC991EA8440}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-52120" yWindow="2960" windowWidth="27220" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Неизменные_короткие" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Этот формат отношений похож</t>
   </si>
@@ -95,6 +95,18 @@
   </si>
   <si>
     <t>расширение отношений чётко не обозначено</t>
+  </si>
+  <si>
+    <t>раздельный бюджет в этой книге не рассматриваю</t>
+  </si>
+  <si>
+    <t>раздельную казну в этой книге не рассматриваю</t>
+  </si>
+  <si>
+    <t>трёхзвёздочного ресторана</t>
+  </si>
+  <si>
+    <t>трёх-звёздочной харчёвни для дворян</t>
   </si>
 </sst>
 </file>
@@ -412,14 +424,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="59.1796875" customWidth="1"/>
-    <col min="2" max="2" width="43.453125" customWidth="1"/>
+    <col min="1" max="1" width="59.140625" customWidth="1"/>
+    <col min="2" max="2" width="52.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -427,7 +439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -435,7 +447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -443,7 +455,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -451,7 +463,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -459,7 +471,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -467,7 +479,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -475,12 +487,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>20</v>
       </c>
       <c r="B8" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -490,14 +510,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4548B0D-7D71-4248-BE5A-4CF5325314DF}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="77.7265625" customWidth="1"/>
-    <col min="2" max="2" width="65.7265625" customWidth="1"/>
+    <col min="1" max="1" width="77.7109375" customWidth="1"/>
+    <col min="2" max="2" width="65.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -505,7 +525,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -513,12 +533,20 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
